--- a/evaluation/evaluation_tables.xlsx
+++ b/evaluation/evaluation_tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Detection Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="False Positives" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Evasion Resistance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cross Framework" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detection Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="False Positives" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evasion Resistance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Level" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,9 +427,9 @@
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -482,25 +482,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>167</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.7547169811320756</v>
       </c>
     </row>
     <row r="3">
@@ -510,25 +510,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>168</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8363636363636363</v>
       </c>
     </row>
     <row r="4">
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.6530612244897959</v>
       </c>
     </row>
     <row r="5">
@@ -566,25 +566,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>173</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.9411764705882353</v>
       </c>
     </row>
     <row r="6">
@@ -598,13 +598,13 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0.8875</v>
+        <v>0.7676739926739927</v>
       </c>
       <c r="G6" t="n">
-        <v>0.95</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9142857142857144</v>
+        <v>0.7963295781434357</v>
       </c>
     </row>
   </sheetData>
@@ -618,13 +618,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="5"/>
@@ -697,18 +697,108 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>command_detector</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>B41, B42, B43, B44, B45, B46, B48, B74</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cookie_validator</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>B80</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>directory_detector</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>sqli_detector</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>B06</t>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>B06, B33, B34, B35, B36, B37, B38, B67</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>user_agent_detector</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>B92, B93</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>xss_detector</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>B55, B56</t>
         </is>
       </c>
     </row>
@@ -1017,866 +1107,334 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Case ID</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Expected Label</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Django Status</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Flask Status</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Django Blocked</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Flask Blocked</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Same Verdict</t>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>FPR</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>200</v>
       </c>
       <c r="C2" t="n">
-        <v>403</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
-        <v>403</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7771428571428572</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>403</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>403</v>
-      </c>
-      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
+      <c r="I3" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8666666666666666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
+          <t>heldout</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>171</v>
       </c>
       <c r="C4" t="n">
-        <v>403</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>403</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>403</v>
-      </c>
-      <c r="D5" t="n">
-        <v>403</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-    </row>
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>81</v>
+      </c>
+      <c r="F4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7953216374269005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8870967741935484</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6626506024096386</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7586206896551725</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.07954545454545454</v>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>Attack Class</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>benign</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>403</v>
-      </c>
-      <c r="D6" t="n">
-        <v>403</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Alerted</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Alert Rate</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Block Rate</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Not Blocked (case IDs)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
+          <t>command_injection</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>403</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CMD04, CMD06, CMD13, CMD14, CMD15, CMD16, CMD19, CMD25</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
+          <t>path_traversal</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>403</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="b">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PATH15, PATH23</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
+          <t>sql_injection</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>403</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>403</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SQL01, SQL04, SQL05, SQL06, SQL07, SQL08, SQL09, SQL11, SQL12, SQL13, SQL15, SQL16, SQL17, SQL18, SQL20, SQL21, SQL22, SQL23</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
+          <t>xss</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>403</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>403</v>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>403</v>
-      </c>
-      <c r="D11" t="n">
-        <v>403</v>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>403</v>
-      </c>
-      <c r="D12" t="n">
-        <v>403</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>B12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>benign</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>403</v>
-      </c>
-      <c r="D13" t="n">
-        <v>403</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SQL01</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>sql_injection</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>403</v>
-      </c>
-      <c r="D14" t="n">
-        <v>403</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SQL02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>sql_injection</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>403</v>
-      </c>
-      <c r="D15" t="n">
-        <v>403</v>
-      </c>
-      <c r="E15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SQL03</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>sql_injection</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>403</v>
-      </c>
-      <c r="D16" t="n">
-        <v>403</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SQL04</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>sql_injection</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>403</v>
-      </c>
-      <c r="D17" t="n">
-        <v>403</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SQL05</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>sql_injection</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>403</v>
-      </c>
-      <c r="D18" t="n">
-        <v>403</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>XSS01</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>xss</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>403</v>
-      </c>
-      <c r="D19" t="n">
-        <v>403</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>XSS02</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>xss</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>403</v>
-      </c>
-      <c r="D20" t="n">
-        <v>403</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>XSS03</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>xss</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>403</v>
-      </c>
-      <c r="D21" t="n">
-        <v>403</v>
-      </c>
-      <c r="E21" t="b">
-        <v>1</v>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>XSS04</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>xss</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>403</v>
-      </c>
-      <c r="D22" t="n">
-        <v>403</v>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>XSS05</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>xss</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>403</v>
-      </c>
-      <c r="D23" t="n">
-        <v>403</v>
-      </c>
-      <c r="E23" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CMD01</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>command_injection</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>403</v>
-      </c>
-      <c r="D24" t="n">
-        <v>403</v>
-      </c>
-      <c r="E24" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>CMD02</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>command_injection</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>403</v>
-      </c>
-      <c r="D25" t="n">
-        <v>403</v>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CMD03</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>command_injection</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>403</v>
-      </c>
-      <c r="D26" t="n">
-        <v>403</v>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>CMD04</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>command_injection</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>403</v>
-      </c>
-      <c r="D27" t="n">
-        <v>403</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PATH01</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>path_traversal</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>403</v>
-      </c>
-      <c r="D28" t="n">
-        <v>403</v>
-      </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PATH02</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>path_traversal</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>403</v>
-      </c>
-      <c r="D29" t="n">
-        <v>403</v>
-      </c>
-      <c r="E29" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PATH03</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>path_traversal</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>403</v>
-      </c>
-      <c r="D30" t="n">
-        <v>403</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Total Cases</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Matching Verdicts</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Consistency Rate</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>XSS08, XSS15, XSS16, XSS25</t>
+        </is>
       </c>
     </row>
   </sheetData>
